--- a/data/trans_orig/P1426-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2012</t>
+          <t>Población con diagnóstico de hipoacusia en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432264</t>
+          <t>431921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305108</t>
+          <t>305184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313383</t>
+          <t>313421</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739403</t>
+          <t>740271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749665</t>
+          <t>749667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13135</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20532</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405662</t>
+          <t>405785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417756</t>
+          <t>416832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>323966</t>
+          <t>324665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336000</t>
+          <t>336094</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736276</t>
+          <t>736775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751736</t>
+          <t>751745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23606</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>27877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605809</t>
+          <t>607132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622660</t>
+          <t>623008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249607</t>
+          <t>249923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259036</t>
+          <t>259056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>862056</t>
+          <t>861667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>879677</t>
+          <t>879496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40416</t>
+          <t>39518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128484</t>
+          <t>1128153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146977</t>
+          <t>1146928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>748762</t>
+          <t>747903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>760861</t>
+          <t>760908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1883315</t>
+          <t>1884213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1906509</t>
+          <t>1905726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19803</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490221</t>
+          <t>489121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>504261</t>
+          <t>503504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740443</t>
+          <t>739976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754590</t>
+          <t>754312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1235563</t>
+          <t>1236827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1255579</t>
+          <t>1255762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>21973</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45866</t>
+          <t>45647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>24056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48308</t>
+          <t>47565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257100</t>
+          <t>257331</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1063485</t>
+          <t>1063704</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1087293</t>
+          <t>1087378</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1327925</t>
+          <t>1328668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1352634</t>
+          <t>1352177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38808</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70244</t>
+          <t>70440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51993</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84827</t>
+          <t>85079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95238</t>
+          <t>98049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141862</t>
+          <t>143457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3351666</t>
+          <t>3351470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3383102</t>
+          <t>3381534</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3462088</t>
+          <t>3461836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3494922</t>
+          <t>3497161</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6826963</t>
+          <t>6825368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6873587</t>
+          <t>6870776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2016</t>
+          <t>Población con diagnóstico de hipoacusia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11964</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>21351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415884</t>
+          <t>416054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427123</t>
+          <t>427130</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335091</t>
+          <t>334679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345055</t>
+          <t>344970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755436</t>
+          <t>754796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770279</t>
+          <t>770199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370207</t>
+          <t>370872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359519</t>
+          <t>359331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371345</t>
+          <t>371344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735714</t>
+          <t>733982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747415</t>
+          <t>747471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505345</t>
+          <t>504346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517176</t>
+          <t>517241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155046</t>
+          <t>155049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164835</t>
+          <t>165023</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664425</t>
+          <t>665201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679948</t>
+          <t>680599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>31090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43323</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1120476</t>
+          <t>1118548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1138500</t>
+          <t>1137706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>805335</t>
+          <t>806537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>819627</t>
+          <t>819985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1932191</t>
+          <t>1933579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1955465</t>
+          <t>1954602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20623</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22371</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37200</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>600083</t>
+          <t>599859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>613616</t>
+          <t>613249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715873</t>
+          <t>716253</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731080</t>
+          <t>731332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1321750</t>
+          <t>1321905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341886</t>
+          <t>1341868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23013</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46617</t>
+          <t>46754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46055</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1035408</t>
+          <t>1035271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1059012</t>
+          <t>1059089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1323115</t>
+          <t>1322477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1346376</t>
+          <t>1346942</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36375</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65693</t>
+          <t>63507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56813</t>
+          <t>56755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91953</t>
+          <t>91456</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101157</t>
+          <t>99665</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146507</t>
+          <t>145998</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3320029</t>
+          <t>3322215</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3349347</t>
+          <t>3348388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3439643</t>
+          <t>3440140</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3474783</t>
+          <t>3474841</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6770811</t>
+          <t>6771320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6816161</t>
+          <t>6817653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2023</t>
+          <t>Población con diagnóstico de hipoacusia en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15052</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31333</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25617</t>
+          <t>26635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46748</t>
+          <t>46336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473879</t>
+          <t>473581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490160</t>
+          <t>490547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425025</t>
+          <t>426483</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>438033</t>
+          <t>438513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>905931</t>
+          <t>906343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>927062</t>
+          <t>926044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>14628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21998</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40017</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420933</t>
+          <t>422143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437004</t>
+          <t>437585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367893</t>
+          <t>367378</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376794</t>
+          <t>376927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>793947</t>
+          <t>792753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>811966</t>
+          <t>811541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44157</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629677</t>
+          <t>628924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661961</t>
+          <t>660245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155285</t>
+          <t>155156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162831</t>
+          <t>162752</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790299</t>
+          <t>789490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823631</t>
+          <t>822523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>49544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75369</t>
+          <t>76366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61636</t>
+          <t>58830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106553</t>
+          <t>105965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>958278</t>
+          <t>957281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>983990</t>
+          <t>984103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>939656</t>
+          <t>941535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964266</t>
+          <t>965122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1903796</t>
+          <t>1904384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1948713</t>
+          <t>1951519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33976</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37236</t>
+          <t>36488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62729</t>
+          <t>61936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59846</t>
+          <t>59861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89687</t>
+          <t>90388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440073</t>
+          <t>440341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456586</t>
+          <t>457123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>775636</t>
+          <t>776429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801129</t>
+          <t>801877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1222726</t>
+          <t>1222025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1252567</t>
+          <t>1252552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>462</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>63149</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41458</t>
+          <t>41948</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65310</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235237</t>
+          <t>235016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240017</t>
+          <t>240045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>698944</t>
+          <t>697543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>720452</t>
+          <t>720669</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>935890</t>
+          <t>935931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>959742</t>
+          <t>959252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120748</t>
+          <t>117504</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>177813</t>
+          <t>178497</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128939</t>
+          <t>124387</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181199</t>
+          <t>178053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>263090</t>
+          <t>262006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>344924</t>
+          <t>344892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3195360</t>
+          <t>3194676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3252425</t>
+          <t>3255669</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3390689</t>
+          <t>3393835</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3442949</t>
+          <t>3447501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6600137</t>
+          <t>6600169</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6681971</t>
+          <t>6683055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1426-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431921</t>
+          <t>431983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305184</t>
+          <t>304738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313421</t>
+          <t>313344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740271</t>
+          <t>740289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749667</t>
+          <t>749683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405785</t>
+          <t>406607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416832</t>
+          <t>416890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324665</t>
+          <t>324952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336094</t>
+          <t>336011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736775</t>
+          <t>736463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751745</t>
+          <t>751708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607132</t>
+          <t>606787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623008</t>
+          <t>623116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249923</t>
+          <t>250357</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259056</t>
+          <t>259060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>861667</t>
+          <t>860454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>879496</t>
+          <t>879462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>31433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>18328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39518</t>
+          <t>41270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128153</t>
+          <t>1127576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146928</t>
+          <t>1146829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>747903</t>
+          <t>749114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>760908</t>
+          <t>761689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1884213</t>
+          <t>1882461</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1905726</t>
+          <t>1905403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489121</t>
+          <t>489817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>503504</t>
+          <t>503484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739976</t>
+          <t>740067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754312</t>
+          <t>754709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1236827</t>
+          <t>1236261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1255762</t>
+          <t>1254984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21973</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45647</t>
+          <t>47489</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24056</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47565</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257331</t>
+          <t>258302</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1063704</t>
+          <t>1061862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1087378</t>
+          <t>1086450</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1328668</t>
+          <t>1327417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1352177</t>
+          <t>1352208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>39301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70440</t>
+          <t>73525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85079</t>
+          <t>83050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98049</t>
+          <t>96609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143457</t>
+          <t>141415</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3351470</t>
+          <t>3348385</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3381534</t>
+          <t>3382609</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3461836</t>
+          <t>3463865</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3497161</t>
+          <t>3495555</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6825368</t>
+          <t>6827410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6870776</t>
+          <t>6872216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21351</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416054</t>
+          <t>415028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427130</t>
+          <t>426950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334679</t>
+          <t>334585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344970</t>
+          <t>344914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>754796</t>
+          <t>756078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770199</t>
+          <t>770353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370872</t>
+          <t>369780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359331</t>
+          <t>359967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371344</t>
+          <t>371343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733982</t>
+          <t>733959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747471</t>
+          <t>747409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504346</t>
+          <t>504803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517241</t>
+          <t>517203</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155049</t>
+          <t>155578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165023</t>
+          <t>165002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665201</t>
+          <t>664729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680599</t>
+          <t>679744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20912</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41935</t>
+          <t>42225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1118548</t>
+          <t>1119616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1137706</t>
+          <t>1137801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>806537</t>
+          <t>805497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>819985</t>
+          <t>819706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1933579</t>
+          <t>1933289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1954602</t>
+          <t>1954627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20847</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>36549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>599859</t>
+          <t>599884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>613249</t>
+          <t>613688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716253</t>
+          <t>717190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731332</t>
+          <t>731760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1321905</t>
+          <t>1322401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341868</t>
+          <t>1342750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22936</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46754</t>
+          <t>46023</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46693</t>
+          <t>48206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1035271</t>
+          <t>1036002</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1059089</t>
+          <t>1059840</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1322477</t>
+          <t>1320964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1346942</t>
+          <t>1345452</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37334</t>
+          <t>36676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63507</t>
+          <t>64464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56755</t>
+          <t>56542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91456</t>
+          <t>94505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>99142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145998</t>
+          <t>144484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3322215</t>
+          <t>3321258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3348388</t>
+          <t>3349046</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3440140</t>
+          <t>3437091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3474841</t>
+          <t>3475054</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6771320</t>
+          <t>6772834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6817653</t>
+          <t>6818176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>32921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14301</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46336</t>
+          <t>51214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>483750</t>
+          <t>527681</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473581</t>
+          <t>517697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490547</t>
+          <t>535086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>433166</t>
+          <t>472036</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426483</t>
+          <t>464111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>438513</t>
+          <t>477558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>916916</t>
+          <t>999716</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906343</t>
+          <t>987815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>926044</t>
+          <t>1009669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>31457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30452</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>43189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>430342</t>
+          <t>460502</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422143</t>
+          <t>451755</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437585</t>
+          <t>467527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>373170</t>
+          <t>412469</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367378</t>
+          <t>406991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376927</t>
+          <t>416470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>803512</t>
+          <t>872971</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>792753</t>
+          <t>861837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>811541</t>
+          <t>881423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381751</t>
+          <t>421814</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381751</t>
+          <t>421814</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381751</t>
+          <t>421814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833964</t>
+          <t>905026</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833964</t>
+          <t>905026</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833964</t>
+          <t>905026</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38621</t>
+          <t>32026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11755</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>645938</t>
+          <t>448253</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628924</t>
+          <t>438717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660245</t>
+          <t>455856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159926</t>
+          <t>179998</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155156</t>
+          <t>174574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162752</t>
+          <t>183447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>805863</t>
+          <t>628252</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789490</t>
+          <t>618616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>822523</t>
+          <t>636576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,22 +7026,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61410</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49544</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76366</t>
+          <t>83511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25540</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>86950</t>
+          <t>94521</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>78310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105965</t>
+          <t>112135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>972237</t>
+          <t>1063778</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>957281</t>
+          <t>1047164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>984103</t>
+          <t>1076460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>951162</t>
+          <t>832134</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>941535</t>
+          <t>824007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965122</t>
+          <t>839019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1923399</t>
+          <t>1895911</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1904384</t>
+          <t>1878297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1951519</t>
+          <t>1912122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033647</t>
+          <t>1130675</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033647</t>
+          <t>1130675</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033647</t>
+          <t>1130675</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976702</t>
+          <t>859758</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976702</t>
+          <t>859758</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976702</t>
+          <t>859758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010349</t>
+          <t>1990432</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010349</t>
+          <t>1990432</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010349</t>
+          <t>1990432</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>18294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33708</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>55026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>45332</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61936</t>
+          <t>66350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>75342</t>
+          <t>79913</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59861</t>
+          <t>68566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90388</t>
+          <t>93337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>449537</t>
+          <t>542089</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440341</t>
+          <t>531976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>457123</t>
+          <t>548682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>787535</t>
+          <t>774412</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>776429</t>
+          <t>763088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801877</t>
+          <t>784106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1237071</t>
+          <t>1316501</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1222025</t>
+          <t>1303077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1252552</t>
+          <t>1327848</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829438</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829438</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312413</t>
+          <t>1396414</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312413</t>
+          <t>1396414</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312413</t>
+          <t>1396414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>500</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40023</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63149</t>
+          <t>67598</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,22 +7782,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>51838</t>
+          <t>56058</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41948</t>
+          <t>45318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>70355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>238710</t>
+          <t>235337</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235016</t>
+          <t>231166</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240045</t>
+          <t>236728</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>710651</t>
+          <t>789429</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>697543</t>
+          <t>775998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>720669</t>
+          <t>799386</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,27 +7895,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>949362</t>
+          <t>1024766</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>935931</t>
+          <t>1010469</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>959252</t>
+          <t>1035506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>152659</t>
+          <t>161813</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117504</t>
+          <t>140832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178497</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>156279</t>
+          <t>170037</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124387</t>
+          <t>150518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>178053</t>
+          <t>190422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>308938</t>
+          <t>331850</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>262006</t>
+          <t>302899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>344892</t>
+          <t>361366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3220514</t>
+          <t>3277639</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3194676</t>
+          <t>3254531</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3255669</t>
+          <t>3298620</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3415609</t>
+          <t>3460477</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3393835</t>
+          <t>3440092</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3447501</t>
+          <t>3479996</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6636123</t>
+          <t>6738116</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6600169</t>
+          <t>6708600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6683055</t>
+          <t>6767067</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373173</t>
+          <t>3439452</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373173</t>
+          <t>3439452</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373173</t>
+          <t>3439452</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3571888</t>
+          <t>3630514</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3571888</t>
+          <t>3630514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3571888</t>
+          <t>3630514</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6945061</t>
+          <t>7069966</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6945061</t>
+          <t>7069966</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6945061</t>
+          <t>7069966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
